--- a/reductions-lit/data/dilution_data_extra.xlsx
+++ b/reductions-lit/data/dilution_data_extra.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28827"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/reductions/data/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://aarhusuniversitet-my.sharepoint.com/personal/au583430_uni_au_dk/Documents/Documents/GitHub/GD-NH3/reductions-lit/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1" documentId="8_{A159C0DB-AC25-4DE9-8CEC-DA3CD6C5DB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B8F490A3-43F2-4686-969E-D67FEA9849B9}"/>
+  <xr:revisionPtr revIDLastSave="51" documentId="8_{A159C0DB-AC25-4DE9-8CEC-DA3CD6C5DB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3FB5D6F2-A512-4992-923B-0F2FB8CBFA4F}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{122F0065-8602-49EC-B7E3-7261009AF15D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{122F0065-8602-49EC-B7E3-7261009AF15D}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="2" r:id="rId1"/>
@@ -36,14 +36,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="309" uniqueCount="73">
   <si>
     <t>Table 5</t>
   </si>
   <si>
-    <t>Stevens et al. 1992</t>
-  </si>
-  <si>
     <t>D20</t>
   </si>
   <si>
@@ -62,9 +59,6 @@
     <t>D140</t>
   </si>
   <si>
-    <t>Mkhabela et al. 2009</t>
-  </si>
-  <si>
     <t>doi:10.1016/j.agee.2008.11.012</t>
   </si>
   <si>
@@ -131,9 +125,6 @@
     <t>splash plate</t>
   </si>
   <si>
-    <t>Frost et al. 1994</t>
-  </si>
-  <si>
     <t>app rate of slurry solids = 0.8 ton/ha</t>
   </si>
   <si>
@@ -203,9 +194,6 @@
     <t>Spitalhof 2</t>
   </si>
   <si>
-    <t>Freibauer and Knöferl 2025</t>
-  </si>
-  <si>
     <t>doi.org/10.1017/S0021859600012223</t>
   </si>
   <si>
@@ -249,6 +237,24 @@
   </si>
   <si>
     <t>red</t>
+  </si>
+  <si>
+    <t>Mkhabela et al., 2009</t>
+  </si>
+  <si>
+    <t>Stevens et al., 1992</t>
+  </si>
+  <si>
+    <t>Frost et al., 1994</t>
+  </si>
+  <si>
+    <t>Freibauer and Knöferl, 2025</t>
+  </si>
+  <si>
+    <t>dil.facA</t>
+  </si>
+  <si>
+    <t>1:1</t>
   </si>
 </sst>
 </file>
@@ -302,7 +308,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -314,6 +320,9 @@
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" indent="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -650,82 +659,86 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2755324F-EBFB-4825-BA7E-D1F948945CF9}">
-  <dimension ref="A1:N1048552"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:O1048552"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="20.54296875" customWidth="1"/>
-    <col min="2" max="2" width="10.7265625" customWidth="1"/>
-    <col min="3" max="3" width="13.26953125" customWidth="1"/>
-    <col min="4" max="4" width="10.7265625" customWidth="1"/>
-    <col min="5" max="5" width="14.7265625" customWidth="1"/>
+    <col min="1" max="1" width="20.5703125" customWidth="1"/>
+    <col min="2" max="2" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="13.28515625" customWidth="1"/>
+    <col min="4" max="4" width="10.7109375" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
-    <col min="7" max="7" width="14.453125" customWidth="1"/>
-    <col min="9" max="9" width="13" customWidth="1"/>
-    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" customWidth="1"/>
+    <col min="9" max="9" width="9.140625" style="3"/>
+    <col min="10" max="10" width="13" customWidth="1"/>
+    <col min="13" max="13" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="F1" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="G1" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="H1" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="I1" s="8" t="s">
+        <v>71</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>67</v>
+      </c>
+      <c r="B2" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
+        <v>9</v>
+      </c>
+      <c r="E2" t="s">
+        <v>27</v>
+      </c>
+      <c r="F2" t="s">
         <v>10</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>60</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="F1" s="2" t="s">
-        <v>62</v>
-      </c>
-      <c r="G1" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="H1" s="2" t="s">
-        <v>64</v>
-      </c>
-      <c r="I1" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>66</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>67</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>68</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A2" t="s">
-        <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="D2" t="s">
-        <v>11</v>
-      </c>
-      <c r="E2" t="s">
-        <v>29</v>
-      </c>
-      <c r="F2" t="s">
-        <v>12</v>
       </c>
       <c r="G2">
         <v>3.96</v>
@@ -733,44 +746,44 @@
       <c r="H2" s="4">
         <v>0.25</v>
       </c>
-      <c r="I2">
+      <c r="J2">
         <v>8.6</v>
       </c>
-      <c r="J2">
+      <c r="K2">
         <v>6.7</v>
       </c>
-      <c r="K2" t="s">
+      <c r="L2" t="s">
+        <v>25</v>
+      </c>
+      <c r="M2" s="1">
+        <f>(1-(K2/J2))*100</f>
+        <v>22.093023255813947</v>
+      </c>
+      <c r="N2" t="s">
+        <v>0</v>
+      </c>
+      <c r="O2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="3" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>67</v>
+      </c>
+      <c r="B3" t="s">
+        <v>18</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="D3" t="s">
+        <v>9</v>
+      </c>
+      <c r="E3" t="s">
         <v>27</v>
       </c>
-      <c r="L2" s="1">
-        <f>(1-(J2/I2))*100</f>
-        <v>22.093023255813947</v>
-      </c>
-      <c r="M2" t="s">
-        <v>0</v>
-      </c>
-      <c r="N2" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="3" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A3" t="s">
-        <v>8</v>
-      </c>
-      <c r="B3" t="s">
-        <v>20</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="D3" t="s">
-        <v>11</v>
-      </c>
-      <c r="E3" t="s">
-        <v>29</v>
-      </c>
       <c r="F3" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G3">
         <v>2.4900000000000002</v>
@@ -778,44 +791,44 @@
       <c r="H3" s="4">
         <v>0.5</v>
       </c>
-      <c r="I3">
+      <c r="J3">
         <v>2.9</v>
       </c>
-      <c r="J3">
+      <c r="K3">
         <v>2</v>
       </c>
-      <c r="K3" t="s">
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" s="1">
+        <f t="shared" ref="M3:M39" si="0">(1-(K3/J3))*100</f>
+        <v>31.034482758620683</v>
+      </c>
+      <c r="N3" t="s">
+        <v>0</v>
+      </c>
+      <c r="O3" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>67</v>
+      </c>
+      <c r="B4" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="D4" t="s">
+        <v>9</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
       </c>
-      <c r="L3" s="1">
-        <f t="shared" ref="L3:L39" si="0">(1-(J3/I3))*100</f>
-        <v>31.034482758620683</v>
-      </c>
-      <c r="M3" t="s">
-        <v>0</v>
-      </c>
-      <c r="N3" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A4" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="D4" t="s">
-        <v>11</v>
-      </c>
-      <c r="E4" t="s">
-        <v>29</v>
-      </c>
       <c r="F4" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G4">
         <v>2.4900000000000002</v>
@@ -823,44 +836,47 @@
       <c r="H4" s="4">
         <v>1</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J4">
         <v>6</v>
       </c>
-      <c r="J4">
+      <c r="K4">
         <v>4</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
+        <v>25</v>
+      </c>
+      <c r="M4" s="1">
+        <f t="shared" si="0"/>
+        <v>33.333333333333336</v>
+      </c>
+      <c r="N4" t="s">
+        <v>0</v>
+      </c>
+      <c r="O4" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>67</v>
+      </c>
+      <c r="B5" t="s">
+        <v>20</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
         <v>27</v>
       </c>
-      <c r="L4" s="1">
-        <f t="shared" si="0"/>
-        <v>33.333333333333336</v>
-      </c>
-      <c r="M4" t="s">
-        <v>0</v>
-      </c>
-      <c r="N4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C5" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="D5" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" t="s">
-        <v>29</v>
-      </c>
       <c r="F5" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G5">
         <v>2.4900000000000002</v>
@@ -868,44 +884,47 @@
       <c r="H5" s="4">
         <v>1</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J5">
         <v>3.8</v>
       </c>
-      <c r="J5">
+      <c r="K5">
         <v>1.6</v>
       </c>
-      <c r="K5" t="s">
+      <c r="L5" t="s">
+        <v>25</v>
+      </c>
+      <c r="M5" s="1">
+        <f t="shared" si="0"/>
+        <v>57.894736842105267</v>
+      </c>
+      <c r="N5" t="s">
+        <v>0</v>
+      </c>
+      <c r="O5" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="6" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>67</v>
+      </c>
+      <c r="B6" t="s">
+        <v>21</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E6" t="s">
         <v>27</v>
       </c>
-      <c r="L5" s="1">
-        <f t="shared" si="0"/>
-        <v>57.894736842105267</v>
-      </c>
-      <c r="M5" t="s">
-        <v>0</v>
-      </c>
-      <c r="N5" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A6" t="s">
-        <v>8</v>
-      </c>
-      <c r="B6" t="s">
-        <v>23</v>
-      </c>
-      <c r="C6" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="D6" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>29</v>
-      </c>
       <c r="F6" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G6">
         <v>4.7300000000000004</v>
@@ -913,41 +932,44 @@
       <c r="H6" s="4">
         <v>1</v>
       </c>
-      <c r="I6">
+      <c r="I6" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J6">
         <v>35.200000000000003</v>
       </c>
-      <c r="J6">
+      <c r="K6">
         <v>35.1</v>
       </c>
-      <c r="K6" t="s">
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" s="1">
+        <f t="shared" si="0"/>
+        <v>0.28409090909091717</v>
+      </c>
+      <c r="N6" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>67</v>
+      </c>
+      <c r="B7" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
         <v>27</v>
       </c>
-      <c r="L6" s="1">
-        <f t="shared" si="0"/>
-        <v>0.28409090909091717</v>
-      </c>
-      <c r="M6" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A7" t="s">
-        <v>8</v>
-      </c>
-      <c r="B7" t="s">
-        <v>24</v>
-      </c>
-      <c r="C7" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" t="s">
-        <v>29</v>
-      </c>
       <c r="F7" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="G7">
         <v>4.7300000000000004</v>
@@ -955,41 +977,44 @@
       <c r="H7" s="4">
         <v>1</v>
       </c>
-      <c r="I7">
+      <c r="I7" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J7">
         <v>17.100000000000001</v>
       </c>
-      <c r="J7">
+      <c r="K7">
         <v>11.4</v>
       </c>
-      <c r="K7" t="s">
-        <v>27</v>
-      </c>
-      <c r="L7" s="1">
+      <c r="L7" t="s">
+        <v>25</v>
+      </c>
+      <c r="M7" s="1">
         <f t="shared" si="0"/>
         <v>33.333333333333336</v>
       </c>
-      <c r="M7" t="s">
+      <c r="N7" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>68</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="B8" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C8" s="3" t="s">
-        <v>2</v>
-      </c>
       <c r="D8" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F8" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G8">
         <v>10.5</v>
@@ -997,38 +1022,38 @@
       <c r="H8" s="4">
         <v>0.2</v>
       </c>
-      <c r="I8">
+      <c r="J8">
         <v>26</v>
       </c>
-      <c r="J8">
+      <c r="K8">
         <v>24</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
+        <v>26</v>
+      </c>
+      <c r="M8" s="1">
+        <f t="shared" si="0"/>
+        <v>7.6923076923076872</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>68</v>
+      </c>
+      <c r="B9" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D9" t="s">
+        <v>9</v>
+      </c>
+      <c r="E9" t="s">
         <v>28</v>
       </c>
-      <c r="L8" s="1">
-        <f t="shared" si="0"/>
-        <v>7.6923076923076872</v>
-      </c>
-    </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A9" t="s">
-        <v>1</v>
-      </c>
-      <c r="B9" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="C9" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
-      </c>
       <c r="F9" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G9">
         <v>10.5</v>
@@ -1036,35 +1061,35 @@
       <c r="H9" s="4">
         <v>0.4</v>
       </c>
-      <c r="I9">
+      <c r="J9">
         <v>26</v>
       </c>
-      <c r="J9">
+      <c r="K9">
         <v>23</v>
       </c>
-      <c r="L9" s="1">
+      <c r="M9" s="1">
         <f t="shared" si="0"/>
         <v>11.538461538461542</v>
       </c>
     </row>
-    <row r="10" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="B10" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D10" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E10" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F10" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G10">
         <v>10.5</v>
@@ -1072,35 +1097,35 @@
       <c r="H10" s="4">
         <v>0.6</v>
       </c>
-      <c r="I10">
+      <c r="J10">
         <v>26</v>
       </c>
-      <c r="J10">
+      <c r="K10">
         <v>17</v>
       </c>
-      <c r="L10" s="1">
+      <c r="M10" s="1">
         <f t="shared" si="0"/>
         <v>34.615384615384613</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="B11" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D11" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E11" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G11">
         <v>10.5</v>
@@ -1108,35 +1133,35 @@
       <c r="H11" s="4">
         <v>0.8</v>
       </c>
-      <c r="I11">
+      <c r="J11">
         <v>26</v>
       </c>
-      <c r="J11">
+      <c r="K11">
         <v>14</v>
       </c>
-      <c r="L11" s="1">
+      <c r="M11" s="1">
         <f t="shared" si="0"/>
         <v>46.153846153846153</v>
       </c>
     </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="B12" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="D12" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F12" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G12">
         <v>10.5</v>
@@ -1144,35 +1169,38 @@
       <c r="H12" s="4">
         <v>1</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J12">
         <v>26</v>
       </c>
-      <c r="J12">
+      <c r="K12">
         <v>11</v>
       </c>
-      <c r="L12" s="1">
+      <c r="M12" s="1">
         <f t="shared" si="0"/>
         <v>57.692307692307686</v>
       </c>
     </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="B13" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C13" s="3" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D13" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E13" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F13" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G13">
         <v>10.5</v>
@@ -1180,35 +1208,35 @@
       <c r="H13" s="4">
         <v>1.2</v>
       </c>
-      <c r="I13">
+      <c r="J13">
         <v>26</v>
       </c>
-      <c r="J13">
+      <c r="K13">
         <v>12</v>
       </c>
-      <c r="L13" s="1">
+      <c r="M13" s="1">
         <f t="shared" si="0"/>
         <v>53.846153846153847</v>
       </c>
     </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>1</v>
+        <v>68</v>
       </c>
       <c r="B14" s="5" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
       <c r="C14" s="3" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="D14" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E14" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F14" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="G14">
         <v>10.5</v>
@@ -1216,32 +1244,32 @@
       <c r="H14" s="4">
         <v>1.4</v>
       </c>
-      <c r="I14">
+      <c r="J14">
         <v>26</v>
       </c>
-      <c r="J14">
+      <c r="K14">
         <v>8</v>
       </c>
-      <c r="L14" s="1">
+      <c r="M14" s="1">
         <f t="shared" si="0"/>
         <v>69.230769230769226</v>
       </c>
     </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B15" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E15" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F15" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G15">
         <v>10.3</v>
@@ -1249,43 +1277,43 @@
       <c r="H15" s="4">
         <v>0.5</v>
       </c>
-      <c r="I15" s="6">
+      <c r="J15" s="6">
         <f>267/2858*100</f>
         <v>9.3421973407977603</v>
       </c>
-      <c r="J15" s="6">
+      <c r="K15" s="6">
         <f>166/2858*100</f>
         <v>5.808257522743177</v>
       </c>
-      <c r="K15" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" s="1">
+      <c r="L15" t="s">
+        <v>25</v>
+      </c>
+      <c r="M15" s="1">
         <f t="shared" si="0"/>
         <v>37.827715355805246</v>
       </c>
-      <c r="M15" t="s">
+      <c r="N15" t="s">
         <v>0</v>
       </c>
-      <c r="N15" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O15" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B16" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F16" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G16">
         <v>10.3</v>
@@ -1293,43 +1321,46 @@
       <c r="H16" s="4">
         <v>1</v>
       </c>
-      <c r="I16" s="6">
+      <c r="I16" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J16" s="6">
         <f>267/2858*100</f>
         <v>9.3421973407977603</v>
       </c>
-      <c r="J16" s="6">
+      <c r="K16" s="6">
         <f>94/2858*100</f>
         <v>3.2890132960111966</v>
       </c>
-      <c r="K16" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="1">
+      <c r="L16" t="s">
+        <v>25</v>
+      </c>
+      <c r="M16" s="1">
         <f t="shared" si="0"/>
         <v>64.794007490636702</v>
       </c>
-      <c r="M16" t="s">
+      <c r="N16" t="s">
         <v>0</v>
       </c>
-      <c r="N16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="17" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O16" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B17" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="E17" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F17" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G17">
         <v>10.3</v>
@@ -1337,43 +1368,43 @@
       <c r="H17" s="4">
         <v>1.5</v>
       </c>
-      <c r="I17" s="6">
+      <c r="J17" s="6">
         <f>267/2858*100</f>
         <v>9.3421973407977603</v>
       </c>
-      <c r="J17" s="6">
+      <c r="K17" s="6">
         <f>55/2858*100</f>
         <v>1.9244226731980407</v>
       </c>
-      <c r="K17" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" s="1">
+      <c r="L17" t="s">
+        <v>25</v>
+      </c>
+      <c r="M17" s="1">
         <f t="shared" si="0"/>
         <v>79.400749063670403</v>
       </c>
-      <c r="M17" t="s">
+      <c r="N17" t="s">
         <v>0</v>
       </c>
-      <c r="N17" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="18" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O17" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="18" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B18" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E18" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G18">
         <v>10.3</v>
@@ -1381,43 +1412,43 @@
       <c r="H18" s="4">
         <v>0.5</v>
       </c>
-      <c r="I18" s="6">
+      <c r="J18" s="6">
         <f>254/2858*100</f>
         <v>8.8873337998600412</v>
       </c>
-      <c r="J18" s="6">
+      <c r="K18" s="6">
         <f>168/2858*100</f>
         <v>5.8782365290412875</v>
       </c>
-      <c r="K18" t="s">
-        <v>27</v>
-      </c>
-      <c r="L18" s="1">
+      <c r="L18" t="s">
+        <v>25</v>
+      </c>
+      <c r="M18" s="1">
         <f t="shared" si="0"/>
         <v>33.85826771653543</v>
       </c>
-      <c r="M18" t="s">
+      <c r="N18" t="s">
         <v>0</v>
       </c>
-      <c r="N18" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="19" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O18" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B19" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C19" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E19" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F19" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G19">
         <v>10.3</v>
@@ -1425,43 +1456,46 @@
       <c r="H19" s="4">
         <v>1</v>
       </c>
-      <c r="I19" s="6">
+      <c r="I19" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J19" s="6">
         <f>254/2858*100</f>
         <v>8.8873337998600412</v>
       </c>
-      <c r="J19" s="6">
+      <c r="K19" s="6">
         <f>91/2858*100</f>
         <v>3.1840447865640309</v>
       </c>
-      <c r="K19" t="s">
-        <v>27</v>
-      </c>
-      <c r="L19" s="1">
+      <c r="L19" t="s">
+        <v>25</v>
+      </c>
+      <c r="M19" s="1">
         <f t="shared" si="0"/>
         <v>64.173228346456696</v>
       </c>
-      <c r="M19" t="s">
+      <c r="N19" t="s">
         <v>0</v>
       </c>
-      <c r="N19" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="20" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O19" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="20" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B20" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C20" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="E20" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F20" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G20">
         <v>10.3</v>
@@ -1469,43 +1503,43 @@
       <c r="H20" s="4">
         <v>1.5</v>
       </c>
-      <c r="I20" s="6">
+      <c r="J20" s="6">
         <f>254/2858*100</f>
         <v>8.8873337998600412</v>
       </c>
-      <c r="J20" s="6">
+      <c r="K20" s="6">
         <f>58/2858*100</f>
         <v>2.0293911826452065</v>
       </c>
-      <c r="K20" t="s">
-        <v>27</v>
-      </c>
-      <c r="L20" s="1">
+      <c r="L20" t="s">
+        <v>25</v>
+      </c>
+      <c r="M20" s="1">
         <f t="shared" si="0"/>
         <v>77.165354330708652</v>
       </c>
-      <c r="M20" t="s">
+      <c r="N20" t="s">
         <v>0</v>
       </c>
-      <c r="N20" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="21" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O20" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
+        <v>69</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B21" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="E21" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F21" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G21">
         <v>10.3</v>
@@ -1513,43 +1547,43 @@
       <c r="H21" s="4">
         <v>0.5</v>
       </c>
-      <c r="I21" s="6">
+      <c r="J21" s="6">
         <f>174/2858*100</f>
         <v>6.0881735479356189</v>
       </c>
-      <c r="J21" s="6">
+      <c r="K21" s="6">
         <f>148/2858*100</f>
         <v>5.1784464660601817</v>
       </c>
-      <c r="K21" t="s">
-        <v>27</v>
-      </c>
-      <c r="L21" s="1">
+      <c r="L21" t="s">
+        <v>25</v>
+      </c>
+      <c r="M21" s="1">
         <f t="shared" si="0"/>
         <v>14.942528735632187</v>
       </c>
-      <c r="M21" t="s">
+      <c r="N21" t="s">
         <v>0</v>
       </c>
-      <c r="N21" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="22" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O21" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="22" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
+        <v>69</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C22" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B22" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C22" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="E22" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F22" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G22">
         <v>10.3</v>
@@ -1557,43 +1591,46 @@
       <c r="H22" s="4">
         <v>1</v>
       </c>
-      <c r="I22" s="6">
+      <c r="I22" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J22" s="6">
         <f>174/2858*100</f>
         <v>6.0881735479356189</v>
       </c>
-      <c r="J22" s="6">
+      <c r="K22" s="6">
         <f>97/2858*100</f>
         <v>3.3939818054583624</v>
       </c>
-      <c r="K22" t="s">
-        <v>27</v>
-      </c>
-      <c r="L22" s="1">
+      <c r="L22" t="s">
+        <v>25</v>
+      </c>
+      <c r="M22" s="1">
         <f t="shared" si="0"/>
         <v>44.252873563218387</v>
       </c>
-      <c r="M22" t="s">
+      <c r="N22" t="s">
         <v>0</v>
       </c>
-      <c r="N22" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="23" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O22" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="23" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
+        <v>69</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B23" s="7" t="s">
-        <v>57</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>34</v>
-      </c>
       <c r="E23" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F23" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G23">
         <v>10.3</v>
@@ -1601,43 +1638,43 @@
       <c r="H23" s="4">
         <v>1.5</v>
       </c>
-      <c r="I23" s="6">
+      <c r="J23" s="6">
         <f>174/2858*100</f>
         <v>6.0881735479356189</v>
       </c>
-      <c r="J23" s="6">
+      <c r="K23" s="6">
         <f>66/2858*100</f>
         <v>2.3093072078376489</v>
       </c>
-      <c r="K23" t="s">
-        <v>27</v>
-      </c>
-      <c r="L23" s="1">
+      <c r="L23" t="s">
+        <v>25</v>
+      </c>
+      <c r="M23" s="1">
         <f t="shared" si="0"/>
         <v>62.068965517241367</v>
       </c>
-      <c r="M23" t="s">
+      <c r="N23" t="s">
         <v>0</v>
       </c>
-      <c r="N23" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O23" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B24" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F24" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G24">
         <v>10.3</v>
@@ -1645,43 +1682,43 @@
       <c r="H24" s="4">
         <v>0.5</v>
       </c>
-      <c r="I24" s="6">
+      <c r="J24" s="6">
         <f>118/2858*100</f>
         <v>4.1287613715885234</v>
       </c>
-      <c r="J24" s="6">
+      <c r="K24" s="6">
         <f>92/2858*100</f>
         <v>3.2190342897130861</v>
       </c>
-      <c r="K24" t="s">
-        <v>27</v>
-      </c>
-      <c r="L24" s="1">
+      <c r="L24" t="s">
+        <v>25</v>
+      </c>
+      <c r="M24" s="1">
         <f t="shared" si="0"/>
         <v>22.033898305084744</v>
       </c>
-      <c r="M24" t="s">
+      <c r="N24" t="s">
         <v>0</v>
       </c>
-      <c r="N24" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O24" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="25" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B25" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C25" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E25" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F25" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G25">
         <v>10.3</v>
@@ -1689,43 +1726,46 @@
       <c r="H25" s="4">
         <v>1</v>
       </c>
-      <c r="I25" s="6">
+      <c r="I25" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J25" s="6">
         <f>118/2858*100</f>
         <v>4.1287613715885234</v>
       </c>
-      <c r="J25" s="6">
+      <c r="K25" s="6">
         <f>59/2858*100</f>
         <v>2.0643806857942617</v>
       </c>
-      <c r="K25" t="s">
-        <v>27</v>
-      </c>
-      <c r="L25" s="1">
+      <c r="L25" t="s">
+        <v>25</v>
+      </c>
+      <c r="M25" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M25" t="s">
+      <c r="N25" t="s">
         <v>0</v>
       </c>
-      <c r="N25" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="26" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O25" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="26" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>31</v>
+        <v>69</v>
       </c>
       <c r="B26" s="7" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="E26" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F26" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G26">
         <v>10.3</v>
@@ -1733,40 +1773,40 @@
       <c r="H26" s="4">
         <v>1.5</v>
       </c>
-      <c r="I26" s="6">
+      <c r="J26" s="6">
         <f>118/2858*100</f>
         <v>4.1287613715885234</v>
       </c>
-      <c r="J26" s="6">
+      <c r="K26" s="6">
         <f>48/2858*100</f>
         <v>1.6794961511546536</v>
       </c>
-      <c r="K26" t="s">
-        <v>27</v>
-      </c>
-      <c r="L26" s="1">
+      <c r="L26" t="s">
+        <v>25</v>
+      </c>
+      <c r="M26" s="1">
         <f t="shared" si="0"/>
         <v>59.322033898305079</v>
       </c>
-      <c r="M26" t="s">
+      <c r="N26" t="s">
         <v>0</v>
       </c>
-      <c r="N26" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="27" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="O26" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="27" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="E27" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F27" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G27">
         <v>8</v>
@@ -1774,38 +1814,38 @@
       <c r="H27" s="4">
         <v>0.5</v>
       </c>
-      <c r="I27">
+      <c r="J27">
         <v>37</v>
       </c>
-      <c r="J27">
+      <c r="K27">
         <v>24</v>
       </c>
-      <c r="K27" t="s">
-        <v>27</v>
-      </c>
-      <c r="L27" s="1">
+      <c r="L27" t="s">
+        <v>25</v>
+      </c>
+      <c r="M27" s="1">
         <f t="shared" si="0"/>
         <v>35.13513513513513</v>
       </c>
-      <c r="M27" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N27" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="28" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N27" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>41</v>
+        <v>38</v>
       </c>
       <c r="E28" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F28" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G28">
         <v>8</v>
@@ -1813,38 +1853,41 @@
       <c r="H28" s="4">
         <v>1</v>
       </c>
-      <c r="I28">
+      <c r="I28" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J28">
         <v>37</v>
       </c>
-      <c r="J28">
+      <c r="K28">
         <v>23</v>
       </c>
-      <c r="K28" t="s">
-        <v>27</v>
-      </c>
-      <c r="L28" s="1">
+      <c r="L28" t="s">
+        <v>25</v>
+      </c>
+      <c r="M28" s="1">
         <f t="shared" si="0"/>
         <v>37.837837837837839</v>
       </c>
-      <c r="M28" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N28" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="29" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N28" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O28" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="29" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
+        <v>36</v>
+      </c>
+      <c r="C29" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="C29" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="E29" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F29" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G29">
         <v>8</v>
@@ -1852,38 +1895,38 @@
       <c r="H29" s="4">
         <v>2</v>
       </c>
-      <c r="I29">
+      <c r="J29">
         <v>37</v>
       </c>
-      <c r="J29">
+      <c r="K29">
         <v>15</v>
       </c>
-      <c r="K29" t="s">
-        <v>27</v>
-      </c>
-      <c r="L29" s="1">
+      <c r="L29" t="s">
+        <v>25</v>
+      </c>
+      <c r="M29" s="1">
         <f t="shared" si="0"/>
         <v>59.459459459459453</v>
       </c>
-      <c r="M29" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N29" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="30" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N29" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O29" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="30" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="E30" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F30" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G30">
         <v>8</v>
@@ -1891,38 +1934,38 @@
       <c r="H30" s="4">
         <v>0.5</v>
       </c>
-      <c r="I30">
+      <c r="J30">
         <v>40</v>
       </c>
-      <c r="J30">
+      <c r="K30">
         <v>28</v>
       </c>
-      <c r="K30" t="s">
-        <v>27</v>
-      </c>
-      <c r="L30" s="1">
+      <c r="L30" t="s">
+        <v>25</v>
+      </c>
+      <c r="M30" s="1">
         <f t="shared" si="0"/>
         <v>30.000000000000004</v>
       </c>
-      <c r="M30" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N30" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="31" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N30" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O30" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="31" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>44</v>
+        <v>41</v>
       </c>
       <c r="E31" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F31" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G31">
         <v>8</v>
@@ -1930,38 +1973,41 @@
       <c r="H31" s="4">
         <v>1</v>
       </c>
-      <c r="I31">
+      <c r="I31" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J31">
         <v>40</v>
       </c>
-      <c r="J31">
+      <c r="K31">
         <v>26</v>
       </c>
-      <c r="K31" t="s">
-        <v>27</v>
-      </c>
-      <c r="L31" s="1">
+      <c r="L31" t="s">
+        <v>25</v>
+      </c>
+      <c r="M31" s="1">
         <f t="shared" si="0"/>
         <v>35</v>
       </c>
-      <c r="M31" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N31" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="32" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N31" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O31" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="32" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>45</v>
+        <v>42</v>
       </c>
       <c r="E32" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F32" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G32">
         <v>8</v>
@@ -1969,38 +2015,38 @@
       <c r="H32" s="4">
         <v>2</v>
       </c>
-      <c r="I32">
+      <c r="J32">
         <v>40</v>
       </c>
-      <c r="J32">
+      <c r="K32">
         <v>18</v>
       </c>
-      <c r="K32" t="s">
-        <v>27</v>
-      </c>
-      <c r="L32" s="1">
+      <c r="L32" t="s">
+        <v>25</v>
+      </c>
+      <c r="M32" s="1">
         <f t="shared" si="0"/>
         <v>55.000000000000007</v>
       </c>
-      <c r="M32" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N32" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="33" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N32" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O32" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="33" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C33" t="s">
-        <v>46</v>
+        <v>43</v>
       </c>
       <c r="E33" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F33" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G33">
         <v>8</v>
@@ -2008,38 +2054,38 @@
       <c r="H33" s="4">
         <v>0.5</v>
       </c>
-      <c r="I33">
+      <c r="J33">
         <v>46</v>
       </c>
-      <c r="J33">
-        <v>33</v>
-      </c>
-      <c r="K33" t="s">
-        <v>27</v>
-      </c>
-      <c r="L33" s="1">
+      <c r="K33">
+        <v>33</v>
+      </c>
+      <c r="L33" t="s">
+        <v>25</v>
+      </c>
+      <c r="M33" s="1">
         <f t="shared" si="0"/>
         <v>28.260869565217394</v>
       </c>
-      <c r="M33" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N33" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N33" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O33" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="34" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C34" t="s">
-        <v>47</v>
+        <v>44</v>
       </c>
       <c r="E34" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F34" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G34">
         <v>8</v>
@@ -2047,38 +2093,41 @@
       <c r="H34" s="4">
         <v>1</v>
       </c>
-      <c r="I34">
+      <c r="I34" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J34">
         <v>46</v>
       </c>
-      <c r="J34">
+      <c r="K34">
         <v>31</v>
       </c>
-      <c r="K34" t="s">
-        <v>27</v>
-      </c>
-      <c r="L34" s="1">
+      <c r="L34" t="s">
+        <v>25</v>
+      </c>
+      <c r="M34" s="1">
         <f t="shared" si="0"/>
         <v>32.608695652173914</v>
       </c>
-      <c r="M34" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N34" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="35" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N34" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O34" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="35" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>39</v>
+        <v>36</v>
       </c>
       <c r="C35" t="s">
-        <v>48</v>
+        <v>45</v>
       </c>
       <c r="E35" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F35" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G35">
         <v>8</v>
@@ -2086,38 +2135,38 @@
       <c r="H35" s="4">
         <v>2</v>
       </c>
-      <c r="I35">
+      <c r="J35">
         <v>46</v>
       </c>
-      <c r="J35">
-        <v>25</v>
-      </c>
-      <c r="K35" t="s">
-        <v>27</v>
-      </c>
-      <c r="L35" s="1">
+      <c r="K35">
+        <v>25</v>
+      </c>
+      <c r="L35" t="s">
+        <v>25</v>
+      </c>
+      <c r="M35" s="1">
         <f t="shared" si="0"/>
         <v>45.652173913043484</v>
       </c>
-      <c r="M35" s="1" t="s">
-        <v>49</v>
-      </c>
-      <c r="N35" t="s">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="36" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N35" s="1" t="s">
+        <v>46</v>
+      </c>
+      <c r="O35" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="36" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="E36" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F36" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G36">
         <v>7.4</v>
@@ -2125,35 +2174,38 @@
       <c r="H36" s="4">
         <v>1</v>
       </c>
-      <c r="I36">
+      <c r="I36" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J36">
         <v>17</v>
       </c>
-      <c r="J36">
+      <c r="K36">
         <v>7</v>
       </c>
-      <c r="K36" t="s">
-        <v>27</v>
-      </c>
-      <c r="L36" s="1">
+      <c r="L36" t="s">
+        <v>25</v>
+      </c>
+      <c r="M36" s="1">
         <f t="shared" si="0"/>
         <v>58.82352941176471</v>
       </c>
-      <c r="M36" s="1" t="s">
+      <c r="N36" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A37" t="s">
+        <v>70</v>
+      </c>
+      <c r="C37" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="37" spans="1:14" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>55</v>
-      </c>
-      <c r="C37" t="s">
-        <v>52</v>
-      </c>
       <c r="E37" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F37" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G37">
         <v>7.4</v>
@@ -2161,35 +2213,38 @@
       <c r="H37" s="4">
         <v>1</v>
       </c>
-      <c r="I37">
+      <c r="I37" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J37">
         <v>3</v>
       </c>
-      <c r="J37">
+      <c r="K37">
         <v>1</v>
       </c>
-      <c r="K37" t="s">
-        <v>27</v>
-      </c>
-      <c r="L37" s="1">
+      <c r="L37" t="s">
+        <v>25</v>
+      </c>
+      <c r="M37" s="1">
         <f t="shared" si="0"/>
         <v>66.666666666666671</v>
       </c>
-      <c r="M37" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="38" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N37" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C38" t="s">
-        <v>53</v>
+        <v>50</v>
       </c>
       <c r="E38" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F38" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G38">
         <v>7.4</v>
@@ -2197,35 +2252,38 @@
       <c r="H38" s="4">
         <v>1</v>
       </c>
-      <c r="I38">
+      <c r="I38" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J38">
         <v>10</v>
       </c>
-      <c r="J38">
+      <c r="K38">
         <v>5</v>
       </c>
-      <c r="K38" t="s">
-        <v>27</v>
-      </c>
-      <c r="L38" s="1">
+      <c r="L38" t="s">
+        <v>25</v>
+      </c>
+      <c r="M38" s="1">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-      <c r="M38" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="39" spans="1:14" x14ac:dyDescent="0.35">
+      <c r="N38" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="39" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="C39" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="E39" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F39" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="G39">
         <v>7.4</v>
@@ -2233,24 +2291,27 @@
       <c r="H39" s="4">
         <v>1</v>
       </c>
-      <c r="I39">
+      <c r="I39" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="J39">
         <v>22</v>
       </c>
-      <c r="J39">
+      <c r="K39">
         <v>8</v>
       </c>
-      <c r="K39" t="s">
-        <v>27</v>
-      </c>
-      <c r="L39" s="1">
+      <c r="L39" t="s">
+        <v>25</v>
+      </c>
+      <c r="M39" s="1">
         <f t="shared" si="0"/>
         <v>63.636363636363633</v>
       </c>
-      <c r="M39" s="1" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="1048552" spans="3:3" x14ac:dyDescent="0.35">
+      <c r="N39" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="1048552" spans="3:3" x14ac:dyDescent="0.25">
       <c r="C1048552" s="3"/>
     </row>
   </sheetData>
